--- a/solutions/demo/closing-engine/template.xlsx
+++ b/solutions/demo/closing-engine/template.xlsx
@@ -2808,7 +2808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2825,6 +2825,7 @@
     <col width="7" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2898,6 +2899,11 @@
           <t>停车费</t>
         </is>
       </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>住民税(无特别征收填 none)</t>
+        </is>
+      </c>
     </row>
     <row r="2" hidden="1">
       <c r="A2" t="inlineStr">
@@ -2968,6 +2974,11 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>commute_parking</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>juminzei_method</t>
         </is>
       </c>
     </row>

--- a/solutions/demo/closing-engine/template.xlsx
+++ b/solutions/demo/closing-engine/template.xlsx
@@ -2821,7 +2821,7 @@
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="7" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
-          <t>通勤方式(car/transit)</t>
+          <t>通勤方式(transit/car/mixed)</t>
         </is>
       </c>
       <c r="L1" s="3" t="inlineStr">

--- a/solutions/demo/closing-engine/template.xlsx
+++ b/solutions/demo/closing-engine/template.xlsx
@@ -30,6 +30,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法人税" sheetId="21" state="visible" r:id="rId21"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="法人税调整" sheetId="22" state="visible" r:id="rId22"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中间纳付" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="科目表" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,13 +50,21 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="13"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -65,6 +74,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E0E7FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9C3"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,13 +94,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -449,61 +483,209 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="0016A34A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>公司资料（月结引擎 · 日本）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <t>公司资料（月结工具・日本）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>公司资料.xlsx：把这个工作簿和银行流水（bank/ 文件夹，网银下载的 CSV 或 Excel）放在同一个文件夹，选择这个文件夹即可。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>按顺序填写：公司 → 方针 → 支给项目 → 银行账户 → 员工（标准报酬・住民税・固定工资）→ 期初余额。其余的表有需要时再填。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>这本工作簿是月结工具的「输入」：公司的基本情况、员工、期初余额、每月的工资和开票，都填在这里。填好以后，把它和银行流水一起放进页面的「表格」入口，工具就会算工资、对银行、做分录和报表。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>怎么填</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>第 2 行是程序用的栏名（已隐藏），不要改。从第 3 行开始填。空着的表 = 没有这项。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+          <t>· 每张表最上面一行，说明这张表是什么、什么时候要填、不填会怎样。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>日期写 2026-04-30，月份写 2026-04（Excel 自动变成日期也没关系）。金额只写数字。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+          <t>· 栏名下面的灰色小字，说明这一栏填什么，并给了一个例子。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>「方针」表的每一项都要选，并写判断人和日期——本产品不替你选默认值，判断会记进底稿的「判断记录」。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+          <t>· 能选的栏有下拉列表：点一下格子，右边出现小三角，从里面选。「科目」「员工ID」这类栏也有下拉，但可以自己打字。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>每月：在「每月工资」写与名册不同的部分（加班・时薪等），在「开票」写当月的请求书。结账后「待确认」的回答写在「回答」表。</t>
+          <t>· 日期写成 2026-04-30，月份写成 2026-04（Excel 自动改成日期格式也没关系）。金额只写数字，不要写「円」和逗号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>· 一张表空着，意思是「公司没有这件事」。如果是「有，但现在不知道」，请先去找资料，不要空着。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>· 不要删除或改名任何一张表，不要改栏名那一行，也不要在表的中间插入空行以外的说明文字。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>一定要填的 6 张表（标签是蓝色的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>① 公司　　　公司名、决算月、从哪个月开始记账、发薪日等。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>② 方针　　　记账上的各项做法（社保怎么扣、消费税怎么算…）。每一项都要选。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>③ 支给项目　工资单上有哪些项目。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>④ 银行账户　有哪些银行账户，流水文件里各列叫什么名字。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>⑤ 员工　　　领工资的每一个人。同时按情况填「标准报酬」「住民税」「固定工资」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>⑥ 期初余额　开始记账月的前一个月月末的試算表。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>有这件事才填的表（标签是灰色的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>每个月都可能要填：每月工资（加班等变动）、奖金、开票（請求書）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>有就填：银行规则（固定收付，填了可以少被问）、固定资产、折旧分摊、调整分录、追加科目。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>特定月份才填：劳动保险（期间里有 6〜7 月）、法人税・法人税调整・中间纳付（期间里有决算月）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>不用手填：回答（在页面上回答后自动写入）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>常见的疑问</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>问：银行流水放在哪里？　答：不用在这本工作簿里写。把网银下载的 CSV 或 Excel 直接放进页面的「表格」入口，工具会按「银行账户」表里登记的列名，认出是哪个账户的。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>问：一笔钱要记成两个科目怎么办（还借款＝本金＋利息；客户扣了手续费才付款；付报酬时扣了源泉所得税）？　答：不要写进「银行规则」。先结账，那一笔会出现在「待确认」里，在页面上点「回答」，就可以拆成几行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>问：不经过银行的交易怎么记（例如社长先垫付的费用、月末的计提）？　答：写在「调整分录」表。之后公司把钱还给社长的那一笔银行付款，用「银行规则」或回答，记到调整分录里用的那个负债科目（未払金 等）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>问：要用的科目，下拉里没有？　答：先看最后一页「科目表」有没有叫法不同的同一个科目；确实没有，就在「追加科目」表里登记一行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>问：资料上找不到某个数字？　答：不要估计着填。说明里一般写了这个数字印在哪份文件上；找不到就先空着，工具会在结账前或结账后明确告诉你缺什么。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>问：填错了会怎样？　答：结账前工具会检查一遍，告诉你是哪张表、第几行、什么问题。改好、保存、关掉 Excel，再点一次「执行结账」即可，可以反复改。</t>
         </is>
       </c>
     </row>
@@ -515,52 +697,90 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="009CA3AF"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="111" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>这张表：每个人每个月固定不变的工资项目和金额。
+什么时候填：月薪制的人必填，一个项目一行。时薪・日薪的人不填这里，每个月在「每月工资」表里填。
+不填的话：既没有固定工资、当月又没填「每月工资」的人，结账后会来问你。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>员工ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>支给项目</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
     </row>
-    <row r="2" hidden="1">
-      <c r="A2" t="inlineStr">
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>「员工」表里的员工ID。例：E01</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>「支给项目」表里的项目名。例：基本給</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>每个月的金额。例：280000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>employee</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="A5:A2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='员工'!$A$5:$A$400</formula1>
+    </dataValidation>
+    <dataValidation sqref="B5:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='支给项目'!$A$5:$A$200</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -568,63 +788,103 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002563EB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="81" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>这张表：开始记账月的前一个月月末，各个科目的余额——也就是那个月末的試算表（残高試算表）。
+什么时候填：【必填】借方合计必须等于贷方合计。如果是会计年度中途开始，損益科目（売上高、給料手当等）从年度初到上个月末的累计也要填。
+不填的话：不填＝所有科目从 0 开始，银行余额和账上余额会对不上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>科目</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>明细</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>借方</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>贷方</t>
         </is>
       </c>
     </row>
-    <row r="2" hidden="1">
-      <c r="A2" t="inlineStr">
+    <row r="3" ht="90" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>科目名（日文）。可以从下拉里选；下拉里没有的，先在「追加科目」表里登记。例：普通預金</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>明细：同一个科目下要分开管的对象。银行存款→银行名（和「银行账户」表一致）；売掛金→客户名；預り金→社会保険料／源泉所得税／住民税／雇用保険；固定资产和減価償却累計額→资产ID。不分就空着。</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>借方余额。资产、费用一般在借方。一行只填借方或贷方其中一边。</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>贷方余额。负债、净资产、收益、減価償却累計額一般在贷方。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>account</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>sub</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>debit</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="A5:A2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='科目表'!$B$2:$B$400</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -632,74 +892,125 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="009CA3AF"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>月(YYYY-MM)</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
+    <row r="1" ht="66" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>这张表：每个月和「固定工资」不一样的部分：加班费、时薪的人当月的工资、入职离职月的日割金额、当月不发的项目。
+什么时候填：有变动的月份才填。
+不填的话：不填＝这个月按「固定工资」原样发。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>员工ID</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>支给项目</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>本月不发(TRUE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" hidden="1">
-      <c r="A2" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>本月不发</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="66" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>发工资的月份。例：2026-06</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>「员工」表里的员工ID。例：E01</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>「支给项目」表里的项目名。例：残業手当</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>这个月这个项目的金额。「固定工资」里有同名项目时，这个月以这里的金额为准。</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>这个月不发这个项目时选「是」（金额空着）。平时空着。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>employee</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>remove</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="B5:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='员工'!$A$5:$A$400</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5:C2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='支给项目'!$A$5:$A$200</formula1>
+    </dataValidation>
+    <dataValidation sqref="E5:E2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请从下拉里选" error="这一栏只能从下拉列表里选一个。" type="list">
+      <formula1>"是"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -707,63 +1018,103 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="009CA3AF"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>月(YYYY-MM)</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
+    <row r="1" ht="81" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>这张表：发奖金（賞与）的月份、支付日和每个人的金额。
+什么时候填：发奖金的月份才填，一人一行。
+不填的话：不填＝没有发奖金。银行流水里的奖金付款会对不上，然后来问你。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>支付日</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>员工ID</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
     </row>
-    <row r="2" hidden="1">
-      <c r="A2" t="inlineStr">
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>发奖金的月份。例：2026-06</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>实际支付的日期。例：2026-06-30</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>「员工」表里的员工ID。例：E01</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>扣税和社保之前的奖金金额。例：300000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>employee</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="C5:C2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='员工'!$A$5:$A$400</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -771,74 +1122,119 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="009CA3AF"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="51" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>这张表：每个月开给客户的請求書（销售收入）。
+什么时候填：有销售的月份都要填，一张請求書一行。
+不填的话：收到了货款却没有对应的請求書，売掛金会变成负数，结账后会来问你。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>客户</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>税区分</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>依据</t>
         </is>
       </c>
     </row>
-    <row r="2" hidden="1">
-      <c r="A2" t="inlineStr">
+    <row r="3" ht="102" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>請求書的日期（算作哪一天的销售）。例：2026-05-31</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>客户名。之后收到这家的货款时，「银行规则」或回答里的「明细」要写同一个名字。例：ナニワ商会</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>請求書上的合计金额（含消费税）。例：1100000</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>消费税的区分，按交易本身的性质选：一般的销售选「課税売上10%」。公司是免税事业者时也这样选，不影响金额。</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>請求書的编号等，方便以后找到原件。例：請求書 No.2026-051</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>customer</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>tax</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>evidence</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="D5:D2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"対象外,課税仕入10%,課税売上10%,非課税仕入,非課税売上"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -846,151 +1242,237 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="009CA3AF"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="51" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>这张表：每个月都会出现的固定收付（房租、货款入账、手续费…）。事先告诉工具「摘要里有这几个字的，就记到这个科目」，以后就不再一笔一笔来问。
+什么时候填：建议填，但不是必须：不填也能结账，只是每一笔流水都会来问你。工资、社会保险、源泉所得税、住民税的付款不用写规则，工具会自己对上；自己公司账户之间的互转也不用写。
+不填的话：一条规则只能指定一个科目。一笔钱要分成两个科目的（还借款＝本金＋利息；客户扣掉手续费后付款；付报酬时扣了源泉所得税），不要写规则，结账后在页面上对那一笔「回答」并拆分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>规则ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>摘要包含</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>方向(out/in)</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>金额(可选)</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>金额（可空）</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>科目</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>明细</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>税区分</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>依据</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I2" s="8" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>判断人</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K2" s="8" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L2" s="8" t="inlineStr">
         <is>
           <t>理由</t>
         </is>
       </c>
     </row>
-    <row r="2" hidden="1">
-      <c r="A2" t="inlineStr">
+    <row r="3" ht="102" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>自己编的规则编号。例：R1</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>流水「摘要」里一定会出现的一段字，照流水原样抄（半角片假名要保持半角）。例：ﾔﾁﾝ</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>这是付出去的钱（出金）还是收进来的钱（入金）。</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>可以空着。只有金额每次都相同、并且想只对这个金额生效时才填。例：132000</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>对方科目：这笔钱记到哪个科目。出金一般是费用（地代家賃 等），入金一般是売掛金。</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>明细（補助科目）：同一个科目下要分开管的对象，例如客户名、银行名。不分就空着。收货款时写客户名（和「开票」表一致）。</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>消费税的区分。空着＝用这个科目默认的区分（见「科目表」）。</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>依据的文件。例：賃貸借契約書</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>这条规则是干什么的，给自己看。例：办公室房租</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>谁做的这个判断（姓名）。【必填】</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>哪一天做的判断。记不清就填填表的当天。【必填】例：2026-05-01</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>为什么这样处理。可以空着，但写上以后查起来方便。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>desc_contains</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>direction</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>account</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>sub</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>tax</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>evidence</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>by</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>at</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="C5:C2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请从下拉里选" error="这一栏只能从下拉列表里选一个。" type="list">
+      <formula1>"出金,入金"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E5:E2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='科目表'!$B$2:$B$400</formula1>
+    </dataValidation>
+    <dataValidation sqref="G5:G2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"対象外,課税仕入10%,課税売上10%,非課税仕入,非課税売上"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -998,151 +1480,234 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="009CA3AF"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="51" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>这张表：需要折旧的固定资产台账（固定資産台帳）。
+什么时候填：有固定资产时填，一项资产一行。
+不填的话：账上有固定资产的余额、这里却没有登记，检查会提示「台帐里没有」，而且不会计提折旧。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>资产ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>科目</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>取得价额</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>取得日</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>开始使用日</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>耐用年数</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>方法(straight/declining_200)</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>折旧方法</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
         <is>
           <t>期初累计折旧</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>判断人</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K2" s="8" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L2" s="8" t="inlineStr">
         <is>
           <t>理由</t>
         </is>
       </c>
     </row>
-    <row r="2" hidden="1">
-      <c r="A2" t="inlineStr">
+    <row r="3" ht="102" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>自己编的资产编号。「期初余额」表里这项资产的「明细」也要写这个编号。例：FA01</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>资产的名称。例：印刷機 A</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>资产的科目。例：工具器具備品、機械装置、車両運搬具</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>取得价额。消费税用税込经理就填含税金额，税抜经理就填不含税金额。例：440000</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>买入（取得）的日期。例：2025-11-10</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>开始使用的日期，从这个月起计提折旧。例：2025-11-15</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>耐用年数，按《耐用年数表》。例：电脑 4、普通汽车 6</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>折旧方法。没有向税务署提交过届出的话，建筑物以外的有形资产是「200%定率法」，建筑物・附属设备・无形资产是「定額法」。</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>本会计年度开始时，已经计提的折旧累计金额。本年度新买的资产填 0。</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>谁做的这个判断（姓名）。【必填】</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>哪一天做的判断。记不清就填填表的当天。【必填】例：2026-05-01</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>为什么这样处理。可以空着，但写上以后查起来方便。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>account</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>cost</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>acquired</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>in_service</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>life</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>accumulated_at_fy_start</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>by</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>at</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="C5:C2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='科目表'!$B$2:$B$400</formula1>
+    </dataValidation>
+    <dataValidation sqref="H5:H2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请从下拉里选" error="这一栏只能从下拉列表里选一个。" type="list">
+      <formula1>"定額法,200%定率法"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1150,74 +1715,122 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="009CA3AF"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="66" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>这张表：一项资产的折旧费要分到几个费用科目时用（例如一栋房子一部分自用、一部分出租）。
+什么时候填：一般不用填。
+不填的话：不填＝全部记到減価償却費。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>资产ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>从(YYYY-MM)</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>到(可空)</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>从</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>到（可空）</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>费用科目</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>比例(1, 0.5, 2/3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" hidden="1">
-      <c r="A2" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>比例</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="78" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>「固定资产」表里的资产ID。例：FA01</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>从哪个月开始这样分摊。例：2026-05</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>分摊到哪个月为止。一直这样分就空着。</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>分摊到的费用科目。例：減価償却費</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>这个科目占的比例。例：0.5、2/3。同一项资产同一段期间，各行的比例合计要等于 1。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>asset</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>from</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>to</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>account</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="A5:A2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='固定资产'!$A$5:$A$400</formula1>
+    </dataValidation>
+    <dataValidation sqref="D5:D2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='科目表'!$B$2:$B$400</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1225,140 +1838,221 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="009CA3AF"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>待确认的key</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>处理(book/done)</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
+    <row r="1" ht="51" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>这张表：结账后工具提出的「待确认」事项，以及你对它们的回答。
+什么时候填：一般不用手填：在页面上回答之后，工具会自动写进这张表。
+不填的话：没有回答的事项会一直留在「待确认」里。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>事项编号</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>处理</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>科目</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>明细</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>税区分</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>拆分金额(多行时)</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>拆分金额</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>依据</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>摘要</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I2" s="8" t="inlineStr">
         <is>
           <t>判断人</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K2" s="8" t="inlineStr">
         <is>
           <t>理由</t>
         </is>
       </c>
     </row>
-    <row r="2" hidden="1">
-      <c r="A2" t="inlineStr">
+    <row r="3" ht="150" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>待确认事项的编号（页面和底稿上都有）。一般由工具自动填。</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>「记账」＝告诉工具这一笔记到哪个科目；「已处理」＝这件事已经用别的办法处理好了，不用再问。</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>选「记账」时：对方科目。</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>明细（補助科目）：同一个科目下要分开管的对象，例如客户名、银行名。不分就空着。</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>消费税的区分。空着＝用这个科目默认的区分（见「科目表」）。</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>一笔流水要拆成几个科目时：一个科目一行，编号相同，这一栏填各自的金额（合计要等于那笔流水的金额）。被扣掉的部分填负数：付报酬 89,790＝支払報酬 100,000＋預り金 -10,210。不拆就空着。</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>依据的文件。例：金銭消費貸借契約書・返済予定表</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>分录上的摘要。空着就用流水的摘要。</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>谁做的这个判断（姓名）。【必填】</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>哪一天做的判断。记不清就填填表的当天。【必填】例：2026-05-01</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>为什么这样处理。可以空着，但写上以后查起来方便。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>action</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>account</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>sub</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>tax</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>evidence</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>memo</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>by</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>at</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="B5:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请从下拉里选" error="这一栏只能从下拉列表里选一个。" type="list">
+      <formula1>"记账,已处理"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5:C2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='科目表'!$B$2:$B$400</formula1>
+    </dataValidation>
+    <dataValidation sqref="E5:E2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"対象外,課税仕入10%,課税売上10%,非課税仕入,非課税売上"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1366,184 +2060,285 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="009CA3AF"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="51" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>这张表：工具不会自动生成、需要你自己补的分录：决算整理、计提、更正、不经过银行的交易等。
+什么时候填：需要时才填。同一张分录的每一行写同一个分录ID，借方合计要等于贷方合计。
+不填的话：不填＝没有手工分录。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>分录ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>每月:从</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>每月:到</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>每月:日(end/数字)</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>每月重复：从</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>每月重复：到</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>每月重复：日</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>摘要</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>科目</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>明细</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I2" s="8" t="inlineStr">
         <is>
           <t>借方</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>贷方</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K2" s="8" t="inlineStr">
         <is>
           <t>税区分</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L2" s="8" t="inlineStr">
         <is>
           <t>依据</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M2" s="8" t="inlineStr">
         <is>
           <t>判断人</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N2" s="8" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="O2" s="8" t="inlineStr">
         <is>
           <t>理由</t>
         </is>
       </c>
     </row>
-    <row r="2" hidden="1">
-      <c r="A2" t="inlineStr">
+    <row r="3" ht="78" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>分录的编号。同一张分录的每一行写同一个编号。例：ADJ-2026-06-01</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>分录的日期。例：2026-06-30。每个月都要重复的分录，这一栏空着，填右边三栏。</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>【每月重复的分录才填】从哪个月开始。例：2026-05</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>【每月重复的分录才填】到哪个月为止。一直重复就空着。</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>【每月重复的分录才填】每个月的哪一天：选「月末」，或者写日期的数字。</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>分录的摘要。例：6 月分 家賃収入</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>科目名（日文）。可以从下拉里选；下拉里没有的，先在「追加科目」表里登记。</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>明细（補助科目）：同一个科目下要分开管的对象，例如客户名、银行名。不分就空着。</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>借方金额。一行只填借方或贷方其中一边。</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>贷方金额。</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>消费税的区分。空着＝用这个科目默认的区分（见「科目表」）。</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>依据的文件。例：賃貸借契約書</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>谁做的这个判断（姓名）。【必填】</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>哪一天做的判断。记不清就填填表的当天。【必填】例：2026-05-01</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>为什么这样处理。可以空着，但写上以后查起来方便。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>recurring_from</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>recurring_to</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>recurring_day</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>narration</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>account</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>sub</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>debit</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>credit</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>tax</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>evidence</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>by</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>at</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:O1"/>
+  </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="E5:E2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"月末"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G5:G2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='科目表'!$B$2:$B$400</formula1>
+    </dataValidation>
+    <dataValidation sqref="K5:K2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"対象外,課税仕入10%,課税売上10%,非課税仕入,非課税売上"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1551,62 +2346,69 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002563EB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="98" customWidth="1" min="3" max="3"/>
     <col hidden="1" width="13" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>项目</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>填写</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>公司名</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>公司的正式名称。例：架空印刷株式会社</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>company.name</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>协会けんぽ支部（都道府县）</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>例：東京 / 大阪</t>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>健康保险的都道府县</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>健康保险（协会けんぽ）的保险费率每个都道府县不同。选公司适用的支部所在地，看《保険料納入告知書》或《適用通知書》。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1615,15 +2417,16 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>总公司市区町村</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>法人住民税用，例：大阪市</t>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>总公司所在的市区町村</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>总公司所在的市区町村，计算法人住民税用。例：大阪市</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1632,15 +2435,16 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>健康保险</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>目前只支持 kyoukaikenpo</t>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>健康保险的种类</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>健康保险的种类。目前只支持「协会けんぽ」（全国健康保険協会）；加入健保組合的公司暂时不能用本工具。</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1649,15 +2453,16 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>劳灾保险 事业种类编号</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>例：94</t>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>劳灾保险的事业种类编号</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>劳灾保险的「事業の種類」编号（两位数字）。印在《労働保険 概算・確定保険料申告書》或《労災保険率決定通知書》上。编号不同费率就不同，请照文件填，不要凭印象。例：94（その他の各種事業）</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1666,15 +2471,16 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>雇用保险 事业区分</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>一般の事業 等</t>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>雇用保险的事业区分</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>雇用保险的事业区分。绝大多数公司是「一般の事業」。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1683,28 +2489,34 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>决算月(1〜12)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>决算月（1〜12）</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>决算月，1〜12 的数字。3 月决算就填 3。</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>company.fiscal_year_end_month</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>开始记账月(YYYY-MM)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>期初余额是它前一个月末</t>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>开始记账的月份</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>从哪个月开始用本工具记账。这个月之前的账，用「期初余额」表交接。例：2026-05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1713,15 +2525,16 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>工资截止日</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>end（月末）或数字</t>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>工资的截止日（締日）。月末截止选「月末」，否则填日期的数字。例：20</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1730,15 +2543,16 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>发薪日</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>数字，31=月末</t>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>发工资的日子，填数字。月末发就填 31。例：25</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1747,15 +2561,16 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>发薪日遇休息日</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>before（提前）/ after（顺延）</t>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>发薪日遇到休息日</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>发薪日遇到周末・节假日时，是提前还是顺延。</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1764,15 +2579,16 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>期初余额的日期</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>开始月前一个月末，例：2026-03-31</t>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>期初余额是哪一天的余额：开始记账月的前一个月的最后一天。例：开始月是 2026-05 → 填 2026-04-30</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1781,15 +2597,16 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>摘要关键词：社保</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>逗号分隔，例：ｼﾔｶｲﾎｹﾝ</t>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>流水摘要里的字样：社会保险</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>银行流水里，社会保险费扣款的「摘要」中会出现的字样，照流水原样抄（半角片假名保持半角），多个用逗号隔开。作用：金额对不上时帮助认出是哪一笔。不知道可以先空着。例：ｼﾔｶｲﾎｹﾝ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1798,26 +2615,36 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>摘要关键词：源泉</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>流水摘要里的字样：源泉所得税</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>同上：缴纳源泉所得税时摘要里的字样。例：ｹﾞﾝｾﾝ</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>bank_keywords.gensen</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>摘要关键词：住民税</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>流水摘要里的字样：住民税</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>同上：缴纳住民税时摘要里的字样。例：ｼﾞﾕｳﾐﾝ</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>bank_keywords.jumin</t>
@@ -1825,6 +2652,23 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="5">
+    <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"北海道,青森,岩手,宮城,秋田,山形,福島,茨城,栃木,群馬,埼玉,千葉,東京,神奈川,新潟,富山,石川,福井,山梨,長野,岐阜,静岡,愛知,三重,滋賀,京都,大阪,兵庫,奈良,和歌山,鳥取,島根,岡山,広島,山口,徳島,香川,愛媛,高知,福岡,佐賀,長崎,熊本,大分,宮崎,鹿児島,沖縄"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"协会けんぽ"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"一般の事業,農林水産・清酒製造の事業,建設の事業"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"月末"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"提前到前一个营业日,顺延到后一个营业日"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1832,140 +2676,215 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="009CA3AF"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>年度</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>开始前工资:雇用</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>开始前工资:劳灾</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>上年度概算保险费</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>本人负担扣除额</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>延纳(TRUE/FALSE)</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>今年度见込额(可空)</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>已计提公司负担(可空)</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
+    <row r="1" ht="51" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>这张表：劳动保险（雇用保险＋劳灾保险）每年 6〜7 月「年度更新」时要用的数字。
+什么时候填：结账期间里有 6 月或 7 月时填。照去年的《労働保険 概算・確定保険料申告書》的控え和工资台账填。
+不填的话：不填也能结账，但算不出年度更新要缴的金额，那一笔付款会来问你。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>保险年度</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>开始前工资：雇用保险</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>开始前工资：劳灾</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>上年度概算保険料</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>开始前本人负担扣除额</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>延納</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>今年度工资预计（可空）</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>已计提公司负担（可空）</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
         <is>
           <t>判断人</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K2" s="8" t="inlineStr">
         <is>
           <t>理由</t>
         </is>
       </c>
     </row>
-    <row r="2" hidden="1">
-      <c r="A2" t="inlineStr">
+    <row r="3" ht="114" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>要确定保险费的那个保险年度的开始年。2026 年 6〜7 月申报的是 2025 年度（2025 年 4 月〜2026 年 3 月）→ 填 2025</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>那个保险年度里，开始用本工具记账之前的月份，付给参加雇用保险的人的工资合计。整个保险年度都在开始记账之前，就填全年的合计；全年都在本工具里记的，就填 0。</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>同上，但范围是全体劳动者（役員除外，没有参加雇用保险的人也包括）。</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>去年年度更新时申报并缴纳的概算保険料（申告書上的「概算保険料額」）。【必填】</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>那个保险年度里，开始用本工具之前的月份，从工资里扣下的雇用保险费（本人负担）合计。</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>今年的概算保险费是否分 3 期缴纳（延納）。只有满足条件（概算保险费 40 万日元以上等）时才有效。</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>今年度工资总额的预计。只有预计和上年度相差很大（不到一半或超过 2 倍）时才填，平时空着。</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>方针选了「每月计提」时才填：那个保险年度里，开始用本工具之前已经计提的公司负担部分。</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>谁做的这个判断（姓名）。【必填】</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>哪一天做的判断。记不清就填填表的当天。【必填】例：2026-05-01</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>为什么这样处理。可以空着，但写上以后查起来方便。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>fiscal_year</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>wages_koyou</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>wages_rousai</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>estimate_paid</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>withheld_employee</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>installment</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>estimate_base</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>accrued_employer</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>by</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>at</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="F5:F2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请从下拉里选" error="这一栏只能从下拉列表里选一个。" type="list">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1973,140 +2892,215 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="009CA3AF"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>决算月(YYYY-MM)</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
+    <row r="1" ht="51" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>这张表：年度决算时计算法人税等（法人税・地方法人税・住民税・事业税）要用的数字。
+什么时候填：结账期间里有决算月时填。
+不填的话：不填也能结账，但做不出法人税等的计算表。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>决算月</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>府县 法人税割率</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>府县 均等割(年)</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>府县 均等割（年）</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>事业税超过税率</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>繰越欠損金控除</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>资本金等(可空)</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>从业者数(可空)</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>市区町村(可空)</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>資本金等（可空）</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>従業者数（可空）</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>市区町村（可空）</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
         <is>
           <t>判断人</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K2" s="8" t="inlineStr">
         <is>
           <t>理由</t>
         </is>
       </c>
     </row>
-    <row r="2" hidden="1">
-      <c r="A2" t="inlineStr">
+    <row r="3" ht="78" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>决算月。例：2026-12</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>都道府県民税的「法人税割」税率，小数写法。看都道府县的税率表。例：0.01（＝1%）</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>都道府県民税的「均等割」年额。例：20000</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>法人事业税是否适用超过税率（資本金或所得超过一定规模的公司）。小公司一般选「否」。</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>本年度要抵扣的繰越欠損金。没有填 0。</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>資本金等の額。空着＝用账上的 資本金＋資本準備金。</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>市区町村内的従業者数（算均等割用）。空着＝用「员工」表的人数。</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>市区町村。空着＝用「公司」表里的。</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>谁做的这个判断（姓名）。【必填】</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>哪一天做的判断。记不清就填填表的当天。【必填】例：2026-05-01</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>为什么这样处理。可以空着，但写上以后查起来方便。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>fiscal_year_end</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>pref_houjinzeiwari_rate</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>pref_kintou</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>jigyouzei_excess</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>loss_carryforward</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>capital_and_reserve</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>employees_in_city</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>municipality</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>by</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>at</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="D5:D2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请从下拉里选" error="这一栏只能从下拉列表里选一个。" type="list">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2114,63 +3108,103 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="009CA3AF"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="51" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>这张表：法人税申报时的加算・减算项目（別表四）。
+什么时候填：有申报调整时填。先在「法人税」表里填好那个决算月。
+不填的话：不填＝没有调整，按账上的税前利润计算。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>决算月</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>加算/减算(add/deduct)</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>加算／减算</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>项目</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
     </row>
-    <row r="2" hidden="1">
-      <c r="A2" t="inlineStr">
+    <row r="3" ht="90" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>决算月，要和「法人税」表里的一样。例：2026-12</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>「加算」＝账上是费用但税法上不能扣的（交際費超过限额等）；「减算」＝税法上可以多扣的。</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>调整项目的名称。例：交際費等の損金不算入額</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>金额。例：120000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>fiscal_year_end</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>kind</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B5:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请从下拉里选" error="这一栏只能从下拉列表里选一个。" type="list">
+      <formula1>"加算,减算"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2178,48 +3212,2149 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="009CA3AF"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="81" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>这张表：本年度已经预缴（中間納付）的法人税等。
+什么时候填：有预缴时填。先在「法人税」表里填好那个决算月。
+不填的话：不填＝没有预缴。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>决算月</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>税目</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="54" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>决算月，要和「法人税」表里的一样。例：2026-12</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>税目。例：法人税、地方法人税、法人住民税、法人事業税</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>已经预缴的金额。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>fiscal_year_end</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0016A34A"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>决算月</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>税目</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" hidden="1">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>fiscal_year_end</t>
-        </is>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>科目代码</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>科目名</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>中文科目</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>余额方向</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>默认税区分</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>← 内置的科目表，只供查看和下拉引用，不要改。这里没有的科目，请写在「追加科目」表。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1100</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>item</t>
+          <t>現金</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>库存现金</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>流動資産</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>普通預金</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>银行存款</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>流動資産</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1120</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>当座預金</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>银行存款</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>流動資産</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1130</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>定期預金</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>银行存款</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>流動資産</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>売掛金</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>应收账款</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>流動資産</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1300</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>商品</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>库存商品</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>流動資産</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1400</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>前払費用</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>预付账款</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>流動資産</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>立替金</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>其他应收款</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>流動資産</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1420</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>仮払金</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>其他应收款</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>流動資産</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1430</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>未収入金</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>其他应收款</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>流動資産</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1440</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>仮払消費税等</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>应交税费</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>流動資産</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1500</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>建物</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>固定资产</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>有形固定資産</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1510</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>建物附属設備</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>固定资产</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>有形固定資産</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1520</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>車両運搬具</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>固定资产</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>有形固定資産</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1530</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>工具器具備品</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>固定资产</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>有形固定資産</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1540</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>一括償却資産</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>固定资产</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>有形固定資産</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1590</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>減価償却累計額</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>累计折旧</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>有形固定資産</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>贷方</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1600</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>土地</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>固定资产</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>有形固定資産</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1700</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ソフトウェア</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>无形资产</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>無形固定資産</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1800</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>敷金</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>其他非流动资产</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>投資その他の資産</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1810</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>差入保証金</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>其他非流动资产</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>投資その他の資産</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2100</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>買掛金</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>应付账款</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>流動負債</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>贷方</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2200</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>短期借入金</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>短期借款</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>流動負債</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>贷方</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2300</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>未払金</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>其他应付款</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>流動負債</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>贷方</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2310</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>未払費用</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>其他应付款</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>流動負債</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>贷方</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2320</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>未払法人税等</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>应交税费</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>流動負債</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>贷方</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2330</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>未払消費税等</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>应交税费</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>流動負債</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>贷方</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2400</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>預り金</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>其他应付款</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>流動負債</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>贷方</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2410</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>仮受金</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>其他应付款</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>流動負債</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>贷方</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2420</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>仮受消費税等</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>应交税费</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>流動負債</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>贷方</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2430</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>前受金</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>预收账款</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>流動負債</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>贷方</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2500</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>役員借入金</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>其他应付款</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>固定負債</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>贷方</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2510</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>長期借入金</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>长期借款</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>固定負債</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>贷方</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>3100</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>資本金</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>实收资本</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>株主資本</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>贷方</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>3200</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>資本準備金</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>资本公积</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>株主資本</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>贷方</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>3300</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>繰越利益剰余金</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>未分配利润</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>株主資本</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>贷方</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>4100</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>売上高</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>主营业务收入</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>売上高</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>贷方</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>課税売上10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>4800</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>受取利息</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>财务费用</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>営業外収益</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>贷方</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>非課税売上</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>4810</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>雑収入</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>营业外收入</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>営業外収益</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>贷方</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>課税売上10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>4900</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>固定資産売却益</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>营业外收入</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>特別利益</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>贷方</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>5100</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>仕入高</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>主营业务成本</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>売上原価</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>課税仕入10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>6100</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>役員報酬</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>管理费用</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>販売費及び一般管理費</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>6110</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>給料手当</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>管理费用</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>販売費及び一般管理費</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>6120</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>賞与</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>管理费用</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>販売費及び一般管理費</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>6130</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>法定福利費</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>管理费用</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>販売費及び一般管理費</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>6140</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>福利厚生費</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>管理费用</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>販売費及び一般管理費</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>課税仕入10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>6200</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>旅費交通費</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>管理费用</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>販売費及び一般管理費</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>課税仕入10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>6210</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>通信費</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>管理费用</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>販売費及び一般管理費</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>課税仕入10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>6220</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>管理费用</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>販売費及び一般管理費</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>課税仕入10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>6230</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>事務用品費</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>管理费用</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>販売費及び一般管理費</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>課税仕入10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>6240</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>水道光熱費</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>管理费用</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>販売費及び一般管理費</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>課税仕入10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>6250</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>地代家賃</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>管理费用</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>販売費及び一般管理費</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>課税仕入10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>6260</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>管理费用</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>販売費及び一般管理費</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>課税仕入10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>6270</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>支払報酬</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>管理费用</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>販売費及び一般管理費</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>課税仕入10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>6280</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>租税公課</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>税金及附加</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>販売費及び一般管理費</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>6290</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>減価償却費</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>管理费用</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>販売費及び一般管理費</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>6300</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>広告宣伝費</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>销售费用</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>販売費及び一般管理費</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>課税仕入10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>6310</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>接待交際費</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>管理费用</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>販売費及び一般管理費</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>課税仕入10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>6320</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>会議費</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>管理费用</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>販売費及び一般管理費</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>課税仕入10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>6330</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>保険料</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>管理费用</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>販売費及び一般管理費</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>非課税仕入</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>6340</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>修繕費</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>管理费用</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>販売費及び一般管理費</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>課税仕入10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>6350</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>諸会費</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>管理费用</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>販売費及び一般管理費</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>6390</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>雑費</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>管理费用</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>販売費及び一般管理費</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>課税仕入10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>7100</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>支払利息</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>财务费用</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>営業外費用</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>非課税仕入</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>7110</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>雑損失</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>营业外支出</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>営業外費用</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>8100</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>固定資産除却損</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>营业外支出</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>特別損失</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>9100</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>法人税等</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>所得税费用</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>法人税等</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>借方</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>対象外</t>
         </is>
       </c>
     </row>
@@ -2231,280 +5366,446 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002563EB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
+    <col hidden="1" width="6" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>项目</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>说明与选项</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
+    <row r="1" ht="51" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>这张表：这张表是公司在记账上的各项「做法」。每家公司不一样，工具不会替你猜，所以每一项都要选。
+什么时候填：【必填】每一行在「选择」栏的下拉里选一个，并填「判断人」和「日期」（消费税的后两项按说明，不适用的可以空着）。
+不填的话：有一项没选，结账前就会提示「方针没有填写」，不能结账。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>要决定的事</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>怎么选</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>选择</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>判断人</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>理由</t>
         </is>
       </c>
-    </row>
-    <row r="2" hidden="1">
-      <c r="A2" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+    </row>
+    <row r="3" ht="66" customHeight="1">
+      <c r="A3" s="6" t="inlineStr"/>
+      <c r="B3" s="6" t="inlineStr"/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>点格子，从下拉里选。</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>谁做的这个判断（姓名）。【必填】</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>哪一天做的判断。记不清就填填表的当天。【必填】例：2026-05-01</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>为什么这样处理。可以空着，但写上以后查起来方便。</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4" hidden="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>help</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>by</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>at</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>社会保险费从哪个月的工资里扣</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>看工资单：5 月发的工资里扣的是 4 月份的保险费→「翌月徴収」（大多数公司）；扣的是 5 月份的→「当月徴収」。</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" t="inlineStr">
         <is>
           <t>policies.shaho_collection</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>社会保険料を給与から控除する月：next_month（翌月徴収・前月分を控除）/ same_month（当月分を控除）　选项：next_month / same_month</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>社会保险费（本人负担）不满 1 日元的尾数</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>从工资里扣的公司选第一种（法律规定的原则）。本人用现金交给公司的选第二种。劳资之间另有约定（特約）一律舍去的选第三种。</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>policies.shaho_rounding</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>被保険者負担分の端数：deduct_half_down（法定・給与控除）/ cash_half_up / truncate（特約）　选项：deduct_half_down / cash_half_up / truncate</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>雇用保险费（本人负担）不满 1 日元的尾数</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>和上一项的选法相同，一般选第一种。</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" t="inlineStr">
         <is>
           <t>policies.koyou_rounding</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>雇用保険の被保険者負担分の端数（社保と同じ三択）　选项：deduct_half_down / cash_half_up / truncate</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>子ども・子育て支援金（本人负担）的尾数怎么取整</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>和健康保险费（＋介护保险费）加在一起之后取整，还是单独取整。看工资单上支援金是不是单独列了一行：没有单独列→「合并」。</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" t="inlineStr">
         <is>
           <t>policies.support_rounding</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>子ども・子育て支援金の被保険者負担分を健保（＋介護）と合算して丸めるか、別に丸めるか　选项：with_health / separate</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>雇用保险费率在年度交替时，按哪一天判断用新费率</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>费率每年 4 月可能变。按工资的截止日判断，还是按发薪日判断——照公司一直以来的做法选。</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" t="inlineStr">
         <is>
           <t>policies.koyou_rate_basis</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>雇用保険料率の年度を賃金の締日で判定するか支払日で判定するか（一次資料で未確認——会社の運用を選ぶ）　选项：closing_date / pay_date</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>公司负担的社会保险费，什么时候记成费用</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>「当月计提」＝每个月末把当月份记成未払費用（符合会计准则，推荐）；「缴纳时」＝下个月末实际扣款时才记费用（简便做法）。</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" t="inlineStr">
         <is>
           <t>policies.shaho_expense</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>会社負担の社会保険料：accrual（その月分を月末に未払費用で計上）/ on_payment（納付時に費用）　选项：accrual / on_payment</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>公司负担的劳动保险费，什么时候记成费用</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>「每月计提」＝每个月按工资估算记成未払費用，年度更新时精算（符合会计准则）；「缴纳时」＝年度更新缴款时一次记费用（金额小时的简便做法）。</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>policies.labor_insurance_expense</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>労働保険の会社負担（雇用保険の事業主分・労災・一般拠出金）：monthly_accrual（毎月の賃金から見積って未払費用に計上）/ on_payment（年度更新の納付時に費用）　选项：monthly_accrual / on_payment</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>源泉所得税是否适用「納期の特例」</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>向税务署提交过《源泉所得税の納期の特例の承認に関する申請書》并获批的公司（员工不满 10 人），半年缴一次（7 月 10 日、1 月 20 日）→「有」。每个月 10 日缴→「没有」。</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" t="inlineStr">
         <is>
           <t>policies.gensen_nouki_tokurei</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>源泉所得税の納期の特例（承認を受けているか）　选项：true / false</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>住民税是否适用「納期の特例」</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>向各市区町村申请并获批的公司，半年缴一次（12 月 10 日、6 月 10 日）→「有」。每个月 10 日缴→「没有」。</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" t="inlineStr">
         <is>
           <t>policies.juminzei_nouki_tokurei</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>住民税の納期の特例（承認を受けているか）　选项：true / false</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>消费税：是课税事业者还是免税事业者</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>登记了インボイス（適格請求書発行事業者）的一定是「课税事业者」。没登记、并且基准期间的课税销售额在 1,000 万日元以下的是「免税事业者」。</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>consumption_tax.status</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>taxable（课税事业者）/ exempt（免税事业者）　选项：taxable / exempt</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>消费税：计算方法</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>只有课税事业者要选。提交过《簡易課税制度選択届出書》的选「简易课税」，否则是「本则课税」。免税事业者空着。</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" t="inlineStr">
         <is>
           <t>consumption_tax.method</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>课税事业者才填：general（本则）/ simplified（简易）　选项：general / simplified</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    </row>
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>消费税：简易课税的事业区分</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>只有选了简易课税才填：第 1 种（批发）〜第 6 种（不动产）。制造业是第 3 种，服务业是第 5 种，照《簡易課税制度選択届出書》或上年的申告書填。其他情况空着。</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" t="inlineStr">
         <is>
           <t>consumption_tax.category</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>简易课税才填：事业区分 1〜6　选项：1 / 2 / 3 / 4 / 5 / 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>消费税：记账方式</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>「税込经理」＝金额含税入账；「税抜经理」＝把消费税单独记到仮払消費税等／仮受消費税等。免税事业者只能选税込经理。</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" t="inlineStr">
         <is>
           <t>consumption_tax.accounting</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>tax_included（税込）/ tax_excluded（税抜）　选项：tax_included / tax_excluded</t>
-        </is>
-      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
   <dataValidations count="13">
-    <dataValidation sqref="C3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"next_month,same_month"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"deduct_half_down,cash_half_up,truncate"</formula1>
-    </dataValidation>
     <dataValidation sqref="C5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"deduct_half_down,cash_half_up,truncate"</formula1>
+      <formula1>"翌月徴収（扣上个月的份）,当月徴収（扣当月的份）"</formula1>
     </dataValidation>
     <dataValidation sqref="C6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"with_health,separate"</formula1>
+      <formula1>"50 銭以下舍去・超过进位（从工资扣）,50 銭未满舍去・以上进位（现金缴）,一律舍去（有特約）"</formula1>
     </dataValidation>
     <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"closing_date,pay_date"</formula1>
+      <formula1>"50 銭以下舍去・超过进位（从工资扣）,50 銭未满舍去・以上进位（现金缴）,一律舍去（有特約）"</formula1>
     </dataValidation>
     <dataValidation sqref="C8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"accrual,on_payment"</formula1>
+      <formula1>"和健康保险费合并后取整,单独取整"</formula1>
     </dataValidation>
     <dataValidation sqref="C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"monthly_accrual,on_payment"</formula1>
+      <formula1>"按工资截止日,按发薪日"</formula1>
     </dataValidation>
     <dataValidation sqref="C10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
+      <formula1>"当月计提（月末记未払費用）,缴纳时记费用"</formula1>
     </dataValidation>
     <dataValidation sqref="C11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
+      <formula1>"每月计提,缴纳时记费用"</formula1>
     </dataValidation>
     <dataValidation sqref="C12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"taxable,exempt"</formula1>
+      <formula1>"有（半年缴一次）,没有（每月缴）"</formula1>
     </dataValidation>
     <dataValidation sqref="C13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"general,simplified"</formula1>
+      <formula1>"有（半年缴一次）,没有（每月缴）"</formula1>
     </dataValidation>
     <dataValidation sqref="C14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"课税事业者,免税事业者"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"本则课税,简易课税"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,3,4,5,6"</formula1>
     </dataValidation>
-    <dataValidation sqref="C15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"tax_included,tax_excluded"</formula1>
+    <dataValidation sqref="C17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"税込经理,税抜经理"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2514,85 +5815,141 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="009CA3AF"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="66" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>这张表：内置科目表（最后一页「科目表」）里没有、而贵公司要用的科目，写在这里。
+什么时候填：在「科目表」里找不到要用的科目时才填。
+不填的话：不填＝只用内置科目。别的表里写了哪里都没有的科目，结账前会提示「科目不在科目表中」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>科目代码</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>科目名</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>区分（営業外収益 等）</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>借贷(debit/credit)</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>余额方向</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>税区分</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>中文科目(可空)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" hidden="1">
-      <c r="A2" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>中文科目（可空）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="126" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>4 位数字，不能和「科目表」里已有的重复。1 开头=资产、2=负债、3=净资产、4=收益、5〜8=费用。例：6990</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>科目名（日文）。之后在别的表里就用这个名字。例：リース料</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>这个科目在报表上归在哪一栏。费用一般选「販売費及び一般管理費」。</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>余额通常在哪一边。资产・费用选「借方」；负债・净资产・收益选「贷方」。</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>这个科目默认的消费税区分。例：リース料→課税仕入10%；利息→非課税仕入；工资・税金→対象外</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>对应的中文科目名。可以空着，只在中日双语的底稿上显示。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>section</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>tax</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>cn</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="C5:C2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"流動資産,有形固定資産,無形固定資産,投資その他の資産,流動負債,固定負債,株主資本,売上高,営業外収益,特別利益,売上原価,販売費及び一般管理費,営業外費用,特別損失,法人税等"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D5:D2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请从下拉里选" error="这一栏只能从下拉列表里选一个。" type="list">
+      <formula1>"借方,贷方"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E5:E2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"対象外,課税仕入10%,課税売上10%,非課税仕入,非課税売上"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2600,74 +5957,128 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002563EB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="51" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>这张表：工资单上有哪些项目（基本給、通勤手当…），各自记到哪个科目、算不算税。
+什么时候填：【必填】工资单上出现过的项目，一个项目一行。
+不填的话：「固定工资」「每月工资」里写了这里没有的项目，结账时会报错。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>支给项目名</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>科目</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>课税</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>算雇用保险工资</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>非课税检查(commute)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" hidden="1">
-      <c r="A2" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>算所得税</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>算雇用保险</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>非课税限额检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="126" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>项目名，和工资单上的叫法一致。例：基本給、役員報酬、通勤手当、残業手当</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>这个项目的费用记到哪个科目。例：従業員的基本給→給料手当；役員的→役員報酬；通勤手当→旅費交通費</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>要不要计入所得税（源泉）的计算。一般选「是」；通勤手当（限额内不课税）选「否」。</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>要不要计入雇用保险的工资。雇用保险按工资总额计算，通勤手当也算在内，所以一般都选「是」。只发给役員的项目（役員報酬）选哪个都不影响计算。</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>只有通勤手当选「通勤手当」：工具会按「员工」表里的通勤方式核对非课税限额。其他项目空着。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>account</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>taxable</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>koyou_wage</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>nontaxable_check</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <dataValidations count="4">
+    <dataValidation sqref="B5:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='科目表'!$B$2:$B$400</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5:C2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请从下拉里选" error="这一栏只能从下拉列表里选一个。" type="list">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D5:D2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请从下拉里选" error="这一栏只能从下拉列表里选一个。" type="list">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E5:E2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请从下拉里选" error="这一栏只能从下拉列表里选一个。" type="list">
+      <formula1>"通勤手当"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2675,129 +6086,167 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002563EB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="51" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>这张表：公司有哪些银行账户，以及每个账户的流水文件里，各列叫什么名字。
+什么时候填：【必填】一个账户一行，有几个账户填几行。
+不填的话：没有登记的账户，它的流水工具认不出来。流水文件本身不用在这里写位置，放进页面的「表格」入口即可。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>账户ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>科目</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>银行名</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>流水文件位置</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>表头:日期</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>表头:摘要</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>表头:出金</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>表头:入金</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>表头:余额</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>日期格式</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" hidden="1">
-      <c r="A2" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>流水的列名：日期</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>流水的列名：摘要</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>流水的列名：出金</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>流水的列名：入金</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>流水的列名：余额</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="90" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>自己起的简短代号，用英文字母或数字。例：main、net。提示信息里会用它指这个账户。</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>这个账户在账上的科目。例：普通預金、当座預金</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>银行名，用来区分多个账户。要和「期初余额」表里这个账户那一行的「明细」写得一模一样。例：架空信金</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>打开这个账户的流水文件（网银下载的 CSV 或 Excel），把第一行里表示「日期」的那一列的名字原样抄过来。例：取引日</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>同上：表示「摘要／内容」的那一列的名字。例：摘要、お取引内容</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>同上：表示「支出金额」的那一列的名字。例：お支払金額。★如果流水里只有一列金额、用正负号区分收支，这一栏和「入金」栏填同一个列名。</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>同上：表示「收入金额」的那一列的名字。例：お預り金額</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>同上：表示「余额」的那一列的名字。例：残高</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>account</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>sub</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>files</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>out</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>in</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>balance</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>date_format</t>
-        </is>
-      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B5:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='科目表'!$B$2:$B$400</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2805,184 +6254,294 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002563EB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="7" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="51" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>这张表：领工资的每一个人（役員和従業員）的基本情况，用来算社会保险、雇用保险和所得税。
+什么时候填：【必填】一人一行。已经离职、但开始记账月以后还发过工资的人也要写。
+不填的话：不在这张表里的人，不会计算工资。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>员工ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>显示名</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>身份(officer/employee)</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>身份</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>出生日期</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>入职日</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>离职日</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>社保</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>社会保险</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>雇用保险</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>源泉栏(kou/otsu)</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>源泉栏</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>扶养人数</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>通勤方式(transit/car/mixed)</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>单程km</t>
-        </is>
-      </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>月定期</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>通勤方式</t>
+        </is>
+      </c>
+      <c r="L2" s="8" t="inlineStr">
+        <is>
+          <t>单程公里</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>月定期券</t>
+        </is>
+      </c>
+      <c r="N2" s="8" t="inlineStr">
         <is>
           <t>停车费</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>住民税(无特别征收填 none)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" hidden="1">
-      <c r="A2" t="inlineStr">
+      <c r="O2" s="8" t="inlineStr">
+        <is>
+          <t>住民税</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="102" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>自己编的代号，别的表用它指这个人。例：E01</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>底稿上显示的名字。可以写姓名，也可以写代号。</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>役員（董事等）还是従業員。役員不参加雇用保险和劳灾保险。</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>出生日期。用来判断 40 岁（开始交介护保险）、65 岁、70 岁等年龄。例：1985-04-15</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>入职日。看雇用契約書或《資格取得確認通知書》。例：2020-04-01</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>离职日。在职就空着。例：2026-06-30</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>是否参加健康保险・厚生年金。看《資格取得確認通知書》。工作时间短、不满足加入条件的人选「未加入」。</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>是否参加雇用保险。役員选「未加入」；每周工作不满 20 小时的人一般也是「未加入」。</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>所得税的源泉栏。向公司交了《扶養控除等申告書》的人选「甲欄」，没交的选「乙欄」。</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>《扶養控除等申告書》上的扶养亲属人数（源泉控除対象配偶者＋控除対象扶養親族）。没有填 0。乙欄的人填 0。</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>上下班的方式，用来核对通勤手当的非课税限额。不发通勤手当就空着。</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>开车・骑车通勤时，单程的公里数（决定非课税限额）。例：12</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>坐电车・巴士时，一个月定期券的金额。例：12000</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>开车通勤时，公司负担的停车费（每月）。没有就空着。</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>住民税怎么交。「特別徴収」＝公司从工资里代扣，这时还要在「住民税」表里填每个月的金额；「普通徴収」＝本人自己交，公司不扣。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>display</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>birth</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>hired</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>left</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>shaho</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>koyou</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>wh_column</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>dependents</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>commute_mode</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>commute_one_way_km</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>commute_pass_monthly</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>commute_parking</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>juminzei_method</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:O1"/>
+  </mergeCells>
+  <dataValidations count="6">
+    <dataValidation sqref="C5:C2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请从下拉里选" error="这一栏只能从下拉列表里选一个。" type="list">
+      <formula1>"役員,従業員"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G5:G2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请从下拉里选" error="这一栏只能从下拉列表里选一个。" type="list">
+      <formula1>"加入,未加入"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H5:H2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请从下拉里选" error="这一栏只能从下拉列表里选一个。" type="list">
+      <formula1>"加入,未加入"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I5:I2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请从下拉里选" error="这一栏只能从下拉列表里选一个。" type="list">
+      <formula1>"甲欄,乙欄"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K5:K2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请从下拉里选" error="这一栏只能从下拉列表里选一个。" type="list">
+      <formula1>"电车・巴士,开车・骑车,两者都有"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O5:O2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请从下拉里选" error="这一栏只能从下拉列表里选一个。" type="list">
+      <formula1>"特別徴収,普通徴収"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2990,63 +6549,103 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="009CA3AF"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="81" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>这张表：参加社会保险的人的「標準報酬月額」。健康保险和厚生年金的保险费按它计算。
+什么时候填：参加社保的人必填。金额变更（每年 9 月的定時決定、工资大幅变动后的随時改定）时，新加一行，不要改旧的行。
+不填的话：参加了社保却没有这一项，结账前会提示。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>员工ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>适用月(YYYY-MM)</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>标准报酬月额</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>适用月</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>標準報酬月額</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>依据</t>
         </is>
       </c>
     </row>
-    <row r="2" hidden="1">
-      <c r="A2" t="inlineStr">
+    <row r="3" ht="54" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>「员工」表里的员工ID。例：E01</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>从哪个月的保险费开始用这个金额。例：2025-09</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>通知书上的「標準報酬月額」（健康保険那一栏的金额）。例：300000</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>这个数字是从哪份文件上看到的。例：標準報酬決定通知書（2025 年 9 月）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>employee</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>from</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>evidence</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="A5:A2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='员工'!$A$5:$A$400</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3054,52 +6653,87 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="009CA3AF"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="126" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>这张表：从工资里代扣的住民税（特別徴収）每个月的金额。
+什么时候填：「员工」表里住民税选了「特別徴収」的人必填。照市区町村寄来的《特別徴収税額決定通知書》填，6 月的金额通常和 7 月以后不同，一个月一行。
+不填的话：该填没填的月份，结账后会来问你（不会当成 0）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>员工ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>月(YYYY-MM)</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>月额</t>
         </is>
       </c>
     </row>
-    <row r="2" hidden="1">
-      <c r="A2" t="inlineStr">
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>「员工」表里的员工ID。例：E01</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>从哪个月的工资里扣。例：2026-06</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>那个月要扣的金额。例：12500</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>employee</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="A5:A2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='员工'!$A$5:$A$400</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/solutions/demo/closing-engine/template.xlsx
+++ b/solutions/demo/closing-engine/template.xlsx
@@ -2064,7 +2064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2080,8 +2080,9 @@
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="51" customHeight="1">
@@ -2156,21 +2157,26 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
+          <t>决算整理</t>
+        </is>
+      </c>
+      <c r="N2" s="8" t="inlineStr">
+        <is>
           <t>判断人</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr">
+      <c r="O2" s="8" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="O2" s="8" t="inlineStr">
+      <c r="P2" s="8" t="inlineStr">
         <is>
           <t>理由</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="78" customHeight="1">
+    <row r="3" ht="138" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>分录的编号。同一张分录的每一行写同一个编号。例：ADJ-2026-06-01</t>
@@ -2233,15 +2239,20 @@
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
+          <t>决算整理（第 13 期）的分录选「是」：日期必须是决算月的最后一天。月报里决算月的「本月」不含它，单独列一栏；本年累计里含它。</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
           <t>谁做的这个判断（姓名）。【必填】</t>
         </is>
       </c>
-      <c r="N3" s="6" t="inlineStr">
+      <c r="O3" s="6" t="inlineStr">
         <is>
           <t>哪一天做的判断。记不清就填填表的当天。【必填】例：2026-05-01</t>
         </is>
       </c>
-      <c r="O3" s="6" t="inlineStr">
+      <c r="P3" s="6" t="inlineStr">
         <is>
           <t>为什么这样处理。可以空着，但写上以后查起来方便。</t>
         </is>
@@ -2310,15 +2321,20 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>by</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>at</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
@@ -2326,9 +2342,9 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A1:P1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="E5:E2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"月末"</formula1>
     </dataValidation>
@@ -2337,6 +2353,9 @@
     </dataValidation>
     <dataValidation sqref="K5:K2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"対象外,課税仕入10%,課税売上10%,非課税仕入,非課税売上"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M5:M2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请从下拉里选" error="这一栏只能从下拉列表里选一个。" type="list">
+      <formula1>"是"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/solutions/demo/closing-engine/template.xlsx
+++ b/solutions/demo/closing-engine/template.xlsx
@@ -1842,7 +1842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1853,9 +1853,10 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="51" customHeight="1">
@@ -1910,15 +1911,20 @@
       </c>
       <c r="I2" s="8" t="inlineStr">
         <is>
+          <t>缴款日</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
           <t>判断人</t>
         </is>
       </c>
-      <c r="J2" s="8" t="inlineStr">
+      <c r="K2" s="8" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="K2" s="8" t="inlineStr">
+      <c r="L2" s="8" t="inlineStr">
         <is>
           <t>理由</t>
         </is>
@@ -1967,15 +1973,20 @@
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
+          <t>【预定的缴款（社保・源泉税・住民税）流水里没有、答「已处理」时才填】实际缴款的日期。例：2026-09-16。工具用它判断有没有超过期限。</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
           <t>谁做的这个判断（姓名）。【必填】</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>哪一天做的判断。记不清就填填表的当天。【必填】例：2026-05-01</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>为什么这样处理。可以空着，但写上以后查起来方便。</t>
         </is>
@@ -2024,15 +2035,20 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>paid_on</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>by</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>at</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
@@ -2040,7 +2056,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="B5:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请从下拉里选" error="这一栏只能从下拉列表里选一个。" type="list">
